--- a/ORGANOGRAMA DAS SECRETARIAS CHEFES E DIRETORES - ATUALIZADO 2026-04-20.xlsx
+++ b/ORGANOGRAMA DAS SECRETARIAS CHEFES E DIRETORES - ATUALIZADO 2026-04-20.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="710">
   <si>
     <t xml:space="preserve">ORGANOGRAMA DAS SECRETARIAS</t>
   </si>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">lnunes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor de Divisão Administrativa</t>
+    <t xml:space="preserve">Divisão Administrativa</t>
   </si>
   <si>
     <t xml:space="preserve">FUNDO SOCIAL DE SOLIDARIEDADE</t>
@@ -66,10 +66,10 @@
     <t xml:space="preserve">Ana Claudia Casseb Finato Zuliani</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão Administrativa, Convênios e Captação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Projetos e Ações Sociais</t>
+    <t xml:space="preserve">Divisão Administrativa, Convênios e Captação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Projetos e Ações Sociais</t>
   </si>
   <si>
     <t xml:space="preserve">Bruna Larissa Barbosa Pegoraro</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">blnovo@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Acolhimento  e  Atendimento Social</t>
+    <t xml:space="preserve">Setor  de  Acolhimento  e  Atendimento Social</t>
   </si>
   <si>
     <t xml:space="preserve">Gleici Aparecida da Cruz Pereira</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">rcrepaldi@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Planejamento Estratégico</t>
+    <t xml:space="preserve">Divisão de Planejamento Estratégico</t>
   </si>
   <si>
     <t xml:space="preserve">Kislaine Regina Pimenta de Lima</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">krlima@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Estratégia e Gestão de Prazos</t>
+    <t xml:space="preserve">Setor de Estratégia e Gestão de Prazos</t>
   </si>
   <si>
     <t xml:space="preserve">Raquel Caroline Soficier</t>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">rsoficier@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Metas e Resultados</t>
+    <t xml:space="preserve">Setor de Metas e Resultados</t>
   </si>
   <si>
     <t xml:space="preserve">Ana Julia de Oliveira Pereira</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">ajopereira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Análise  de  Dados  e Indicadores</t>
+    <t xml:space="preserve">Divisão  de  Análise  de  Dados  e Indicadores</t>
   </si>
   <si>
     <t xml:space="preserve">Luana Cristina Neres</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">lcneres@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Monitoramento e Avaliação de Indicadores</t>
+    <t xml:space="preserve">Setor de Monitoramento e Avaliação de Indicadores</t>
   </si>
   <si>
     <t xml:space="preserve">Denis Paulo Santana</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">denis.santana@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor      da      Divisão Conecta+Olímpia</t>
+    <t xml:space="preserve">Divisão Conecta+Olímpia</t>
   </si>
   <si>
     <t xml:space="preserve">de</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">trpimenta@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe      do      Setor Desenvolvimento</t>
+    <t xml:space="preserve">Setor Desenvolvimento</t>
   </si>
   <si>
     <t xml:space="preserve">Treinamento</t>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">e</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Implantação e Melhorias</t>
+    <t xml:space="preserve">Setor de Implantação e Melhorias</t>
   </si>
   <si>
     <t xml:space="preserve">Jessica Barrera Santos</t>
@@ -180,7 +180,7 @@
     <t xml:space="preserve">jbsantos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Governança, Processos e Projetos Estratégicos</t>
+    <t xml:space="preserve">Divisão de Governança, Processos e Projetos Estratégicos</t>
   </si>
   <si>
     <t xml:space="preserve">Tamires Cristina de Toledo Marinho</t>
@@ -189,10 +189,10 @@
     <t xml:space="preserve">tatoledo@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Escritório  de  Processos  e Projetos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Estudos  Estratégicos  e  Boas Práticas da Gestão</t>
+    <t xml:space="preserve">Setor  de  Escritório  de  Processos  e Projetos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Estudos  Estratégicos  e  Boas Práticas da Gestão</t>
   </si>
   <si>
     <t xml:space="preserve">Andressa de Souza Cardoso</t>
@@ -201,13 +201,13 @@
     <t xml:space="preserve">ascardoso@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Normas e Atos Oficiais</t>
+    <t xml:space="preserve">Divisão de Normas e Atos Oficiais</t>
   </si>
   <si>
     <t xml:space="preserve">Cleber Luis Braga</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Normas e Expediente</t>
+    <t xml:space="preserve">Setor de Normas e Expediente</t>
   </si>
   <si>
     <t xml:space="preserve">Edson Lopes da Silva</t>
@@ -216,7 +216,7 @@
     <t xml:space="preserve">elsilva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Assuntos Jurídicos</t>
+    <t xml:space="preserve">Divisão de Assuntos Jurídicos</t>
   </si>
   <si>
     <t xml:space="preserve">Antonio Cataneo Neto</t>
@@ -225,7 +225,7 @@
     <t xml:space="preserve">acneto@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Execuções Fiscais e Assuntos Tributários</t>
+    <t xml:space="preserve">Setor de Execuções Fiscais e Assuntos Tributários</t>
   </si>
   <si>
     <t xml:space="preserve">Débora de Medeiros Passarella</t>
@@ -234,7 +234,7 @@
     <t xml:space="preserve">dmpassarella@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Atos    Administrativos, Consultoria e Pareceres</t>
+    <t xml:space="preserve">Setor    de    Atos    Administrativos, Consultoria e Pareceres</t>
   </si>
   <si>
     <t xml:space="preserve">Cleston Cristiano dos Santos</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">cleston.santos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Acompanhamento    de Licitações, Contratos e Convênios</t>
+    <t xml:space="preserve">Setor    de    Acompanhamento    de Licitações, Contratos e Convênios</t>
   </si>
   <si>
     <t xml:space="preserve">Isabela Duran Oliveira Souza</t>
@@ -252,7 +252,7 @@
     <t xml:space="preserve">idosouza@olimpia.sp.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe     do     Setor     de     Processos     Cíveis, Administrativos e Trabalhistas</t>
+    <t xml:space="preserve">Setor     de     Processos     Cíveis, Administrativos e Trabalhistas</t>
   </si>
   <si>
     <t xml:space="preserve">Priscila Carina Victorasso</t>
@@ -261,7 +261,7 @@
     <t xml:space="preserve">pvictorasso@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor Administrativo</t>
+    <t xml:space="preserve">Setor Administrativo</t>
   </si>
   <si>
     <t xml:space="preserve">Karolina Pessini Moreira Francisco</t>
@@ -279,8 +279,8 @@
     <t xml:space="preserve">claudio.silva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Apoio ao Terceiro Setor e
-Organizações Comunitárias</t>
+    <t xml:space="preserve">Divisão de Apoio ao Terceiro Setor e
+Organizações Comunitária</t>
   </si>
   <si>
     <t xml:space="preserve">Wayne Bergamasco Junior</t>
@@ -289,14 +289,14 @@
     <t xml:space="preserve">wbjunior@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Captação Estratégica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Relações   Federativas   e
+    <t xml:space="preserve">Divisão de Captação Estratégica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de   Relações   Federativas   e
 Investimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor   da   Divisão   de   Parcerias   Público-
+    <t xml:space="preserve">Divisão   de   Parcerias   Público-
 Privadas e Concessões</t>
   </si>
   <si>
@@ -306,10 +306,10 @@
     <t xml:space="preserve">tserafim@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Coordenação e Gestão de PPP e Concessões</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Ouvidoria,  Análise  e
+    <t xml:space="preserve">Setor de Coordenação e Gestão de PPP e Concessões</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão  de  Ouvidoria,  Análise  e
 Resolução de Demandas</t>
   </si>
   <si>
@@ -319,15 +319,15 @@
     <t xml:space="preserve">cppereira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Atendimento, Encaminhamento
+    <t xml:space="preserve">Setor de Atendimento, Encaminhamento
 e Resolução</t>
   </si>
   <si>
     <t xml:space="preserve">Ana Carolina Sadoco Freitas</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Comunicação, Imprensa,
-Cerimonial e Eventos</t>
+    <t xml:space="preserve">Divisão de Comunicação, Imprensa,
+Cerimonial e Evento</t>
   </si>
   <si>
     <t xml:space="preserve">Priscila Fernanda Minani</t>
@@ -336,13 +336,13 @@
     <t xml:space="preserve">pfminani@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Cerimonial e Solenidades</t>
+    <t xml:space="preserve">Setor de Cerimonial e Solenidades</t>
   </si>
   <si>
     <t xml:space="preserve">Maila Najila Batista Ruas</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Imprensa e Marketing</t>
+    <t xml:space="preserve">Setor de Imprensa e Marketing</t>
   </si>
   <si>
     <t xml:space="preserve">Leandro Brito</t>
@@ -360,7 +360,7 @@
     <t xml:space="preserve">edna.silva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Proteção Social Básica</t>
+    <t xml:space="preserve">Divisão de Proteção Social Básica</t>
   </si>
   <si>
     <t xml:space="preserve">Aline Aparecida Caputi</t>
@@ -369,13 +369,13 @@
     <t xml:space="preserve">acpaschoal@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de CRAS I</t>
+    <t xml:space="preserve">Setor de CRAS I</t>
   </si>
   <si>
     <t xml:space="preserve">Erica Oliveira Bittencourt Ferreira</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de CRAS II</t>
+    <t xml:space="preserve">Setor de CRAS II</t>
   </si>
   <si>
     <t xml:space="preserve">Joice Carla Martinussi Simoes</t>
@@ -384,7 +384,7 @@
     <t xml:space="preserve">jcsimoes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de CRAS III</t>
+    <t xml:space="preserve">Setor de CRAS III</t>
   </si>
   <si>
     <t xml:space="preserve">Vanessa Cristina de Oliveira</t>
@@ -393,7 +393,7 @@
     <t xml:space="preserve">vcoliveira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Centro de Convivência do Idoso</t>
+    <t xml:space="preserve">Setor de Centro de Convivência do Idoso</t>
   </si>
   <si>
     <t xml:space="preserve">Rosimeire Aparecida Albertino</t>
@@ -402,7 +402,7 @@
     <t xml:space="preserve">raalbertino@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor do Programa Criança Feliz</t>
+    <t xml:space="preserve">Setor do Programa Criança Feliz</t>
   </si>
   <si>
     <t xml:space="preserve">Patricia Renata Macul Leite de Souza</t>
@@ -411,7 +411,7 @@
     <t xml:space="preserve">prsouza@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Proteção Social Especial</t>
+    <t xml:space="preserve">Divisão de Proteção Social Especial</t>
   </si>
   <si>
     <t xml:space="preserve">Erica Cristina de Jesus Silva</t>
@@ -420,7 +420,7 @@
     <t xml:space="preserve">ecsilva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de CREAS</t>
+    <t xml:space="preserve">Setor de CREAS</t>
   </si>
   <si>
     <t xml:space="preserve">Andressa Recco Barão Santos</t>
@@ -429,19 +429,19 @@
     <t xml:space="preserve">arbarao@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor Centro Dia do Idoso</t>
+    <t xml:space="preserve">Setor Centro Dia do Idoso</t>
   </si>
   <si>
     <t xml:space="preserve">Janaina Carvalho Marin Simões</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor da Casa de Passagem</t>
+    <t xml:space="preserve">Setor da Casa de Passagem</t>
   </si>
   <si>
     <t xml:space="preserve">Eli Simoni Dias Zacharias</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Acolhimento   a   Criança   e Adolescente</t>
+    <t xml:space="preserve">Setor   de   Acolhimento   a   Criança   e Adolescente</t>
   </si>
   <si>
     <t xml:space="preserve">Solange Teresinha Rebellato dos Santos</t>
@@ -450,13 +450,13 @@
     <t xml:space="preserve">stsantos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor do Programa Vida Longa</t>
+    <t xml:space="preserve">Setor do Programa Vida Longa</t>
   </si>
   <si>
     <t xml:space="preserve">Andreia Bignardi Medeiros</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Interesse  Habitacional, Regularização       Fundiária       e       Melhorias
+    <t xml:space="preserve">Divisão  de  Interesse  Habitacional, Regularização       Fundiária       e       Melhorias
 Habitacionais</t>
   </si>
   <si>
@@ -466,7 +466,7 @@
     <t xml:space="preserve">posartori@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Planejamento  e  Programas
+    <t xml:space="preserve">Setor  de  Planejamento  e  Programas
 Habitacionais</t>
   </si>
   <si>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">acabreu@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Gestão Administrativa e Financiamento do SUAS</t>
+    <t xml:space="preserve">Divisão de Gestão Administrativa e Financiamento do SUAS</t>
   </si>
   <si>
     <t xml:space="preserve">Gustavo Sartori Louzada</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">glouzada@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Compras e Controle de Estoque</t>
+    <t xml:space="preserve">Setor de Compras e Controle de Estoque</t>
   </si>
   <si>
     <t xml:space="preserve">Elaine Cristina do Nascimento Estefanini</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Prestação de Contas e Controle Orçamentário</t>
+    <t xml:space="preserve">Setor de Prestação de Contas e Controle Orçamentário</t>
   </si>
   <si>
     <t xml:space="preserve">Gisele Adriana Mendes</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">gamendes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Gerenciamento,  Controle  e Concessão de Benefícios Eventuais</t>
+    <t xml:space="preserve">Setor  de  Gerenciamento,  Controle  e Concessão de Benefícios Eventuais</t>
   </si>
   <si>
     <t xml:space="preserve">Luis Paulo Justino de Oliveira</t>
@@ -509,17 +509,17 @@
     <t xml:space="preserve">lpoliveira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor        da        Divisão        de        Vigilância
+    <t xml:space="preserve">Divisão        de        Vigilância
 Socioassistencial, Cadastro Único e Gestão do Conecta+Olímpia</t>
   </si>
   <si>
     <t xml:space="preserve">Anderson Thiago Mauyama Nascimento</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Monitoramento e Avaliação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Gestão    Executiva   dos
+    <t xml:space="preserve">Setor de Monitoramento e Avaliação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor    de    Gestão    Executiva   dos
 Conselhos</t>
   </si>
   <si>
@@ -529,7 +529,7 @@
     <t xml:space="preserve">asaranda@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Captação de Recursos e
+    <t xml:space="preserve">Divisão de Captação de Recursos e
 Fomento ao Terceiro Setor</t>
   </si>
   <si>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">acampos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Gestão e Fomento do Terceiro
+    <t xml:space="preserve">Setor de Gestão e Fomento do Terceiro
 Setor</t>
   </si>
   <si>
@@ -558,28 +558,25 @@
     <t xml:space="preserve">jrpimenta@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão Administrativa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ivan Paschoaletto Kojima</t>
   </si>
   <si>
     <t xml:space="preserve">ivan.kojima@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio Administrativo</t>
+    <t xml:space="preserve">Setor de Apoio Administrativo</t>
   </si>
   <si>
     <t xml:space="preserve">Robertha Carla Gonçalves Affonso</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Projetos e Eventos</t>
+    <t xml:space="preserve">Setor de Projetos e Eventos</t>
   </si>
   <si>
     <t xml:space="preserve">Kevilin Aiane Andreoli</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Manutenção  de  Prédios  e Suprimentos</t>
+    <t xml:space="preserve">Setor  de  Manutenção  de  Prédios  e Suprimentos</t>
   </si>
   <si>
     <t xml:space="preserve">Solange Cristina da Silva de Souza</t>
@@ -588,7 +585,7 @@
     <t xml:space="preserve">scsouza@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Esporte</t>
+    <t xml:space="preserve">Divisão de Esporte</t>
   </si>
   <si>
     <t xml:space="preserve">Vanessa de Paula Haines Claudino</t>
@@ -597,7 +594,7 @@
     <t xml:space="preserve">vpclaudino@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Coordenação Esportiva</t>
+    <t xml:space="preserve">Setor de Coordenação Esportiva</t>
   </si>
   <si>
     <t xml:space="preserve">Robson Dias Luciano</t>
@@ -625,7 +622,7 @@
     <t xml:space="preserve">cplolo@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Coordenação,   Lazer   e Juventude</t>
+    <t xml:space="preserve">Setor   de   Coordenação,   Lazer   e Juventude</t>
   </si>
   <si>
     <t xml:space="preserve">Fabiano Martins dos Santos</t>
@@ -643,7 +640,7 @@
     <t xml:space="preserve">humberto.puttini@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor        da         Divisão         Administrativa, Planejamento, Desenvolvimento            e Infraestrutura Turística</t>
+    <t xml:space="preserve">Divisão         Administrativa, Planejamento, Desenvolvimento            e Infraestrutura Turística</t>
   </si>
   <si>
     <t xml:space="preserve">Vanessa Lucia Sperandio</t>
@@ -652,7 +649,7 @@
     <t xml:space="preserve">vlsperandio@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  Administrativo  e  Infraestrutura Turística</t>
+    <t xml:space="preserve">Setor  Administrativo  e  Infraestrutura Turística</t>
   </si>
   <si>
     <t xml:space="preserve">Matias Roberto da Silva Costa</t>
@@ -661,7 +658,7 @@
     <t xml:space="preserve">mrcosta@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor   da   Divisão   de   Eventos,   Parcerias, Desenvolvimento   e   Suporte   aos   Atrativos Turísticos</t>
+    <t xml:space="preserve">Divisão   de   Eventos,   Parcerias, Desenvolvimento   e   Suporte   aos   Atrativos Turísticos</t>
   </si>
   <si>
     <t xml:space="preserve">Rodrigo Cesar Borges Marini</t>
@@ -670,7 +667,7 @@
     <t xml:space="preserve">rmarini@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Eventos</t>
+    <t xml:space="preserve">Setor de Eventos</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Cambraia Baptista</t>
@@ -679,7 +676,7 @@
     <t xml:space="preserve">dcbaptista@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Suporte aos Atrativos Turísticos</t>
+    <t xml:space="preserve">Setor de Suporte aos Atrativos Turísticos</t>
   </si>
   <si>
     <t xml:space="preserve">Andréa Christine Torres Trevisanuto</t>
@@ -703,10 +700,10 @@
     <t xml:space="preserve">gmendes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Apoio   Administrativo   e Operacional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor   da   Divisão   de   Patrimônio   Histórico Cultural</t>
+    <t xml:space="preserve">Setor   de   Apoio   Administrativo   e Operacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão   de   Patrimônio   Histórico Cultural</t>
   </si>
   <si>
     <t xml:space="preserve">Tiago Louzada</t>
@@ -715,7 +712,7 @@
     <t xml:space="preserve">tlouzada@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Preservação  do  Patrimônio
+    <t xml:space="preserve">Setor  de  Preservação  do  Patrimônio
 Material    e    Imaterial    e    Coordenação    dos Equipamentos Culturais</t>
   </si>
   <si>
@@ -725,7 +722,7 @@
     <t xml:space="preserve">rsnunes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Festivais e Eventos</t>
+    <t xml:space="preserve">Divisão de Festivais e Eventos</t>
   </si>
   <si>
     <t xml:space="preserve">Camila Reale Thereza Gameiro</t>
@@ -734,7 +731,7 @@
     <t xml:space="preserve">creale@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Planejamento do Calendário de Eventos</t>
+    <t xml:space="preserve">Setor de Planejamento do Calendário de Eventos</t>
   </si>
   <si>
     <t xml:space="preserve">Arian Lourenço de Mello</t>
@@ -743,7 +740,7 @@
     <t xml:space="preserve">almello@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Programas  e  Projetos Culturais</t>
+    <t xml:space="preserve">Divisão  de  Programas  e  Projetos Culturais</t>
   </si>
   <si>
     <t xml:space="preserve">Alan Saviolo Duran</t>
@@ -752,7 +749,7 @@
     <t xml:space="preserve">svduran@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Fomento e Apoio aos Projetos</t>
+    <t xml:space="preserve">Setor de Fomento e Apoio aos Projetos</t>
   </si>
   <si>
     <t xml:space="preserve">Natalia Bortolan Ritzinger</t>
@@ -776,11 +773,11 @@
     <t xml:space="preserve">mmialich@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Agricultura, Inspeção de
+    <t xml:space="preserve">Divisão de Agricultura, Inspeção de
 Produtos de Origem Animal e Patrulha Agrícola Mecanizada</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio aos Produtos de Origem Animal (SIMPOA)</t>
+    <t xml:space="preserve">Setor de Apoio aos Produtos de Origem Animal (SIMPOA)</t>
   </si>
   <si>
     <t xml:space="preserve">Renan Matheus Gerolim Ferreira</t>
@@ -789,7 +786,7 @@
     <t xml:space="preserve">rferreira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Patrulha Agrícola Mecanizada</t>
+    <t xml:space="preserve">Setor de Patrulha Agrícola Mecanizada</t>
   </si>
   <si>
     <t xml:space="preserve">Jean Carlos Siqueira</t>
@@ -798,7 +795,7 @@
     <t xml:space="preserve">jean.siqueira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio às Feiras</t>
+    <t xml:space="preserve">Setor de Apoio às Feiras</t>
   </si>
   <si>
     <t xml:space="preserve">Mara Silvia dos Santos Buzatto</t>
@@ -807,13 +804,13 @@
     <t xml:space="preserve">msbuzatto@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Inovação  Tecnológica, Estudos Econômicos e Pesquisas</t>
+    <t xml:space="preserve">Divisão  de  Inovação  Tecnológica, Estudos Econômicos e Pesquisas</t>
   </si>
   <si>
     <t xml:space="preserve">Anderson Alex Polizel</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Apoio   à   Integração   das Secretarias,  Banco  de  Dados  Integrado  (BDI)  e Geoprocessamento</t>
+    <t xml:space="preserve">Setor   de   Apoio   à   Integração   das Secretarias,  Banco  de  Dados  Integrado  (BDI)  e Geoprocessamento</t>
   </si>
   <si>
     <t xml:space="preserve">João Adriano Nadalin</t>
@@ -822,7 +819,7 @@
     <t xml:space="preserve">joao.nadalin@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Inovação Tecnológica</t>
+    <t xml:space="preserve">Setor de Inovação Tecnológica</t>
   </si>
   <si>
     <t xml:space="preserve">Odécio Luiz de Oliveira Souza</t>
@@ -831,13 +828,13 @@
     <t xml:space="preserve">olsouza@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor    da    Divisão    de    Desenvolvimento Econômico Sustentável</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor da Casa do Empreendedor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio a Indústria e Parceria com
+    <t xml:space="preserve">Divisão    de    Desenvolvimento Econômico Sustentável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor da Casa do Empreendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Apoio a Indústria e Parceria com
 o Sistema “S” Sebrae/Senai/Sesi/Sest/Senat</t>
   </si>
   <si>
@@ -847,7 +844,7 @@
     <t xml:space="preserve">lucio.lucca@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio ao Comércio e Parceria
+    <t xml:space="preserve">Setor de Apoio ao Comércio e Parceria
 com o Sistema “S” Senac/Sebrae/Sest/Senat/Sesc</t>
   </si>
   <si>
@@ -857,7 +854,7 @@
     <t xml:space="preserve">agveronezi@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Estudos, Boletins e Indicadores</t>
+    <t xml:space="preserve">Setor de Estudos, Boletins e Indicadores</t>
   </si>
   <si>
     <t xml:space="preserve">Paulo Rogério Pércio</t>
@@ -866,7 +863,7 @@
     <t xml:space="preserve">ppercio@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor     da     Divisão     de     Atendimento     e Capacitação ao Cidadão</t>
+    <t xml:space="preserve">Divisão     de     Atendimento     e Capacitação ao Cidadão</t>
   </si>
   <si>
     <t xml:space="preserve">Wesley Fernando Freu</t>
@@ -875,7 +872,7 @@
     <t xml:space="preserve">wesley.freu@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Atendimento Poupatempo</t>
+    <t xml:space="preserve">Setor de Atendimento Poupatempo</t>
   </si>
   <si>
     <t xml:space="preserve">Emerson Rodrigo Canevarolo</t>
@@ -884,13 +881,13 @@
     <t xml:space="preserve">ercanevarolo@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Coordenação do Procon</t>
+    <t xml:space="preserve">Setor de Coordenação do Procon</t>
   </si>
   <si>
     <t xml:space="preserve">Carlos Eduardo Moro</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor   de  Capacitação,  Formação  e Aperfeiçoamento</t>
+    <t xml:space="preserve">Setor   de  Capacitação,  Formação  e Aperfeiçoamento</t>
   </si>
   <si>
     <t xml:space="preserve">Audrey Hermes Konda</t>
@@ -914,7 +911,7 @@
     <t xml:space="preserve">famoraes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Frotas e Remoção de Pacientes</t>
+    <t xml:space="preserve">Setor de Frotas e Remoção de Pacientes</t>
   </si>
   <si>
     <t xml:space="preserve">Milton Cesar Delgado Monteiro</t>
@@ -923,7 +920,7 @@
     <t xml:space="preserve">milton.monteiro@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio a Licitação</t>
+    <t xml:space="preserve">Setor de Apoio a Licitação</t>
   </si>
   <si>
     <t xml:space="preserve">Kelly Cristina Araujo Pimenta</t>
@@ -932,14 +929,14 @@
     <t xml:space="preserve">kcpimenta@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio à Informatização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Manutenção  de  Prédios  e
+    <t xml:space="preserve">Setor de Apoio à Informatização</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Manutenção  de  Prédios  e
 Suprimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Apoio   a   Elaboração   de
+    <t xml:space="preserve">Setor   de   Apoio   a   Elaboração   de
 Documentos Técnicos para Processos Licitatórios</t>
   </si>
   <si>
@@ -949,7 +946,7 @@
     <t xml:space="preserve">mmcarvalho@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Planejamento, Avaliação
+    <t xml:space="preserve">Divisão de Planejamento, Avaliação
 e Desenvolvimento</t>
   </si>
   <si>
@@ -959,7 +956,7 @@
     <t xml:space="preserve">ligiane.santos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Fiscalização  de  Contratos  e
+    <t xml:space="preserve">Setor  de  Fiscalização  de  Contratos  e
 Convênios</t>
   </si>
   <si>
@@ -969,7 +966,7 @@
     <t xml:space="preserve">ctkai@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Regulação dos Serviços</t>
+    <t xml:space="preserve">Setor de Regulação dos Serviços</t>
   </si>
   <si>
     <t xml:space="preserve">Gisele Ribeiro José Paschoal</t>
@@ -978,7 +975,7 @@
     <t xml:space="preserve">grpaschoal@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Núcleo   de   Informação, Processamento de Dados e Faturamento</t>
+    <t xml:space="preserve">Setor   de   Núcleo   de   Informação, Processamento de Dados e Faturamento</t>
   </si>
   <si>
     <t xml:space="preserve">Claudemir Fernandes</t>
@@ -987,7 +984,7 @@
     <t xml:space="preserve">claudemir.fernandes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Ação Judicial</t>
+    <t xml:space="preserve">Setor de Ação Judicial</t>
   </si>
   <si>
     <t xml:space="preserve">Marli de Fatima Donadi</t>
@@ -996,7 +993,7 @@
     <t xml:space="preserve">mdonadi@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Gestão   de   Contratos   e Convênios</t>
+    <t xml:space="preserve">Setor   de   Gestão   de   Contratos   e Convênios</t>
   </si>
   <si>
     <t xml:space="preserve">Paulo Júnior Freitas Oliveira</t>
@@ -1005,7 +1002,7 @@
     <t xml:space="preserve">pfreitas@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Auditoria</t>
+    <t xml:space="preserve">Setor de Auditoria</t>
   </si>
   <si>
     <t xml:space="preserve">Isabela Monyse Tassinari</t>
@@ -1015,23 +1012,23 @@
   </si>
   <si>
     <t xml:space="preserve">Diretor da Divisão de Educação Permanente e
-Humanização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Parcerias com Instituições de
+Humanizaçã</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Parcerias com Instituições de
 Ensino, Estágios e Residência Médica</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Ouvidoria SUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Vigilância em Saúde</t>
+    <t xml:space="preserve">Setor de Ouvidoria SUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Vigilância em Saúde</t>
   </si>
   <si>
     <t xml:space="preserve">Niceia Mattos Mussolin</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Vigilância Epidemiológica</t>
+    <t xml:space="preserve">Setor de Vigilância Epidemiológic</t>
   </si>
   <si>
     <t xml:space="preserve">Franciele Cristina de Oliveira Avila</t>
@@ -1040,7 +1037,7 @@
     <t xml:space="preserve">fcavila@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Vigilância Sanitária</t>
+    <t xml:space="preserve">Setor de Vigilância Sanitári</t>
   </si>
   <si>
     <t xml:space="preserve">Evandro Roberto Victorello</t>
@@ -1049,7 +1046,7 @@
     <t xml:space="preserve">ervictorello@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Controle   de   Endemias   e Animais Peçonhentos</t>
+    <t xml:space="preserve">Setor   de   Controle   de   Endemias   e Animais Peçonhentos</t>
   </si>
   <si>
     <t xml:space="preserve">Marco Antonio Cintra</t>
@@ -1058,7 +1055,7 @@
     <t xml:space="preserve">macintra@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor     da     Divisão     de     Média     e     Alta
+    <t xml:space="preserve">Divisão     de     Média     e     Alta
 Complexidade</t>
   </si>
   <si>
@@ -1068,7 +1065,7 @@
     <t xml:space="preserve">aferreira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Ambulatório de Referência de Especialidades – ARE</t>
+    <t xml:space="preserve">Setor de Ambulatório de Referência de Especialidades – ARE</t>
   </si>
   <si>
     <t xml:space="preserve">Lilian Carla Foganhole dos Santos Dias</t>
@@ -1077,13 +1074,13 @@
     <t xml:space="preserve">lcfoganhole@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Diagnóstico Complementar</t>
+    <t xml:space="preserve">Setor de Diagnóstico Complementar</t>
   </si>
   <si>
     <t xml:space="preserve">Gislaine Pimentel Lima</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Saúde Mental</t>
+    <t xml:space="preserve">Setor de Saúde Mental</t>
   </si>
   <si>
     <t xml:space="preserve">Natalia Maria Mazer</t>
@@ -1092,7 +1089,7 @@
     <t xml:space="preserve">nmmazer@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Reabilitação  (EMAD/EMAP) Fisioterapia</t>
+    <t xml:space="preserve">Setor  de  Reabilitação  (EMAD/EMAP) Fisioterapia</t>
   </si>
   <si>
     <t xml:space="preserve">Janaina Gabriela Munhoz Peniani</t>
@@ -1101,7 +1098,7 @@
     <t xml:space="preserve">jgmunhoz@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Atenção Primária</t>
+    <t xml:space="preserve">Diretor da Divisão de Atenção Primári</t>
   </si>
   <si>
     <t xml:space="preserve">Marilia Nogueira Angelo Recio</t>
@@ -1110,7 +1107,7 @@
     <t xml:space="preserve">mrecio@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Distrito Sanitário I</t>
+    <t xml:space="preserve">Setor de Distrito Sanitário I</t>
   </si>
   <si>
     <t xml:space="preserve">Michely Aline Rodrigues do Prado</t>
@@ -1119,7 +1116,7 @@
     <t xml:space="preserve">maprado@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Distrito Sanitário II</t>
+    <t xml:space="preserve">Setor de Distrito Sanitário II</t>
   </si>
   <si>
     <t xml:space="preserve">Amanda Ferrarese</t>
@@ -1131,7 +1128,7 @@
     <t xml:space="preserve">aferrarese@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor Mãe Olimpiense</t>
+    <t xml:space="preserve">Setor Mãe Olimpiense</t>
   </si>
   <si>
     <t xml:space="preserve">Ana Carolina Ferraz Marcondes</t>
@@ -1140,10 +1137,10 @@
     <t xml:space="preserve">acmarcondes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Saúde Bucal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Assistência Farmacêutica
+    <t xml:space="preserve">Setor de Saúde Bucal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Assistência Farmacêutica
 e Insumos Estratégicos</t>
   </si>
   <si>
@@ -1153,7 +1150,7 @@
     <t xml:space="preserve">fvneto@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Suporte    Administrativo Farmacêutico</t>
+    <t xml:space="preserve">Setor    de    Suporte    Administrativo Farmacêutico</t>
   </si>
   <si>
     <t xml:space="preserve">Rosimeire dos Santos Carvalho</t>
@@ -1162,7 +1159,7 @@
     <t xml:space="preserve">rscarvalho@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio à Logística</t>
+    <t xml:space="preserve">Setor de Apoio à Logística</t>
   </si>
   <si>
     <t xml:space="preserve">Evandro Montini Mariano da Silva</t>
@@ -1171,7 +1168,7 @@
     <t xml:space="preserve">emsilva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor   da   Divisão   de   Unidade   de   Pronto
+    <t xml:space="preserve">Divisão   de   Unidade   de   Pronto
 Atendimento UPA 24h</t>
   </si>
   <si>
@@ -1181,7 +1178,7 @@
     <t xml:space="preserve">dpandreoli@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Suporte    Administrativo UPA/SAMU</t>
+    <t xml:space="preserve">Setor    de    Suporte    Administrativo UPA/SAMU</t>
   </si>
   <si>
     <t xml:space="preserve">Daniela Monteiro de Souza</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">jessica.santos@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  Administrativa,  Controle  e
+    <t xml:space="preserve">Divisão  Administrativa,  Controle  e
 Execução Orçamentária</t>
   </si>
   <si>
@@ -1209,13 +1206,13 @@
     <t xml:space="preserve">acmartinussi@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Protocolo</t>
+    <t xml:space="preserve">Setor de Protocolo</t>
   </si>
   <si>
     <t xml:space="preserve">Luciana Perpétua dos Santos</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Apoio   Administrativo   e Monitoramento de Contratos</t>
+    <t xml:space="preserve">Setor   de   Apoio   Administrativo   e Monitoramento de Contratos</t>
   </si>
   <si>
     <t xml:space="preserve">Yasmin Degásperi Fossalussa</t>
@@ -1224,7 +1221,7 @@
     <t xml:space="preserve">ydfossalussa@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Planejamento</t>
+    <t xml:space="preserve">Divisão de Planejamento</t>
   </si>
   <si>
     <t xml:space="preserve">Claudia Roberta Aureliano Pereira</t>
@@ -1236,7 +1233,7 @@
     <t xml:space="preserve">nome diferente no ad</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Demanda Escolar</t>
+    <t xml:space="preserve">Setor de Demanda Escola</t>
   </si>
   <si>
     <t xml:space="preserve">Patrícia Alves Rodrigues Lopes</t>
@@ -1245,7 +1242,7 @@
     <t xml:space="preserve">palopes@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Transporte Escolar</t>
+    <t xml:space="preserve">Setor de Transporte Escola</t>
   </si>
   <si>
     <t xml:space="preserve">Emerson Rangel Polliseli Costa Júnior</t>
@@ -1260,22 +1257,22 @@
     <t xml:space="preserve">jvsilva@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Alimentação Escolar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Oficinas Pedagógicas</t>
+    <t xml:space="preserve">Setor de Alimentação Escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Oficinas Pedagógicas</t>
   </si>
   <si>
     <t xml:space="preserve">Deize Mirela Caputo de Mattos</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Ensino Infantil</t>
+    <t xml:space="preserve">Setor de Ensino Infant</t>
   </si>
   <si>
     <t xml:space="preserve">Claudia Regina Fossalussa Lisse</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Ensino Fundamental</t>
+    <t xml:space="preserve">Setor de Ensino Fundamenta</t>
   </si>
   <si>
     <t xml:space="preserve">Luciane Morais Diogo</t>
@@ -1284,7 +1281,7 @@
     <t xml:space="preserve">lmdiogo@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Educação Especial e Inclusiva</t>
+    <t xml:space="preserve">Setor de Educação Especial e Inclusi</t>
   </si>
   <si>
     <t xml:space="preserve">Marcela Rubia Nespolo Aniceto</t>
@@ -1293,7 +1290,7 @@
     <t xml:space="preserve">mraniceto@olimpia.sp.gov.br </t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Supervisão Escolar</t>
+    <t xml:space="preserve">Divisão de Supervisão Escolar</t>
   </si>
   <si>
     <t xml:space="preserve">Camila Ap. dos Santos Oliveira</t>
@@ -1302,7 +1299,7 @@
     <t xml:space="preserve">caoliveira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino I</t>
+    <t xml:space="preserve">Setor de Supervisão de Ensino </t>
   </si>
   <si>
     <t xml:space="preserve">Silvana Albano</t>
@@ -1311,7 +1308,7 @@
     <t xml:space="preserve">salabano@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino II</t>
+    <t xml:space="preserve">Setor de Supervisão de Ensino I</t>
   </si>
   <si>
     <t xml:space="preserve">Flávia Mialich</t>
@@ -1320,7 +1317,7 @@
     <t xml:space="preserve">flavia.mialich@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino III</t>
+    <t xml:space="preserve">Setor de Supervisão de Ensino II</t>
   </si>
   <si>
     <t xml:space="preserve">Luciana Ferreira de Julle</t>
@@ -1329,16 +1326,13 @@
     <t xml:space="preserve">ldejulle@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino IV</t>
+    <t xml:space="preserve">Setor de Supervisão de Ensino IV</t>
   </si>
   <si>
     <t xml:space="preserve">Luciana Maria M. N. Alves Teixeira</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Supervisão de Ensino VI</t>
+    <t xml:space="preserve">Setor de Supervisão de Ensino V</t>
   </si>
   <si>
     <t xml:space="preserve">Luciana Raphael Diniz Spagnol</t>
@@ -1347,7 +1341,7 @@
     <t xml:space="preserve">ldiniz@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Implantação Tecnológica e Controle Educacional</t>
+    <t xml:space="preserve">Divisão de Implantação Tecnológica e Controle Educacional</t>
   </si>
   <si>
     <t xml:space="preserve">Alisson Filipe Fernandes</t>
@@ -1356,7 +1350,7 @@
     <t xml:space="preserve">affernandes@olimpia.sp.gov.br </t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Implementação  de  Soluções Tecnológicas e Gestão do Conecta+Olímpia</t>
+    <t xml:space="preserve">Setor  de  Implementação  de  Soluções Tecnológicas e Gestão do Conecta+Olímpi</t>
   </si>
   <si>
     <t xml:space="preserve">Elaine Cristina Dias Maciel de Andrade</t>
@@ -1365,7 +1359,7 @@
     <t xml:space="preserve">elaine.maciel@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Formação e Capacitação Digital</t>
+    <t xml:space="preserve">Setor de Formação e Capacitação Digita</t>
   </si>
   <si>
     <t xml:space="preserve">Tiago Pessoa Lourenço</t>
@@ -1383,7 +1377,7 @@
     <t xml:space="preserve">cleber.cisotto@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor da Divisão de Planejamento e Execução
+    <t xml:space="preserve">Divisão de Planejamento e Execução
 Orçamentária</t>
   </si>
   <si>
@@ -1393,10 +1387,10 @@
     <t xml:space="preserve">mscalisse@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Planejamento e Orçamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Execução Orçamentária</t>
+    <t xml:space="preserve">Setor de Planejamento e Orçament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Execução Orçamentári</t>
   </si>
   <si>
     <t xml:space="preserve">Renan Diniz Spagnol</t>
@@ -1405,10 +1399,10 @@
     <t xml:space="preserve">rdspagnol@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Chefe do Setor de Tesouraria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Custos</t>
+    <t xml:space="preserve">Setor de Tesourari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Custos</t>
   </si>
   <si>
     <t xml:space="preserve">Geniana Papani Ferreira</t>
@@ -1417,762 +1411,792 @@
     <t xml:space="preserve">gferreira@olimpia.sp.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Cadastro  e  Gestão  da
+    <t xml:space="preserve">Divisão  de  Cadastro  e  Gestão  da
+Dívida Ativ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela Cardoso da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gcsilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Cadastro Imobiliári</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrícia Bassi Bitencourt Gobbi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pbitencourt@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Cadastro Mobiliári</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrícia de Cássia Velini Bertuolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pcvelini@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Patrimônio Imobiliário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruna Camioto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bcamioto@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Dívida Ativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frederico Camioto Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fcamioto@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Fiscalização Tributári</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renato Luis Pivello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rlpivello@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Tributo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosicler Berti Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rbsantos@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Fiscalização de Postura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deise Cristina Lopes Valério</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dclvalerio@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Postura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleber Luis Gonsaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clgonsaga@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA MUNICIPAL DE GESTÃO E CIDADE INTELIGENTE DECRETO N.º 9.843/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Mena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max.mena@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão  de  Gestão  de  Recursos
+Humanos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandro de Campos Magalhães</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smagalhaes@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Folha de Pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaina Bartholomeu Cordon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tbcordon@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor      de      Treinamento      e     Desenvolvimento Huma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taiga Renata da Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarcruz@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de  Serviço  Especializado  em Segurança e Medicina do Trabalh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michelli da Silva Camargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michelli.camargo@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Gestão  de  Vínculos,  Atos  e Sistemas de Escrituração Digita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isabela Recco de Almeida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">irecco@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Gestão e Planejamento de Compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karolini Escobar de Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kesouza@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Planejamento e Formalização das Contrataçõe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Laura Rosa Machado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">almachado@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thais da Silva Fernandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tsfernandes@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Licitações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carolina Feitosa Ferezin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cfferezin@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Gestão Contratual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Paula Rodrigues Bertolino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arodrigues@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Gestão de Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lígia Dias de oliveira Bianchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ldoliveira@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Fiscalização de Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiane da Fonseca Trinca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dftrinca@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariana Daroz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdaroz@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretor da Divisão de Gestão Logístic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helton Jose Quilles Rodrigues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hjrodrigues@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Almoxarifado e Distribuiçã</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Márcio Gláucio Ribeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgribeiro@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natali Aparecida Souza Camargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nacamargo@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretor da Divisão de Gestão Operaciona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andre Luiz Alves da Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alcosta@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Patrimônio Mobiliário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Mateus A. Martins dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lmasantos@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe  do Setor  de  Controle  e  Manutenção  de Frotas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Apoio e Atendimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio Cezar dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jcsantos@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Tecnologia da Informaçã</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Ishikawa Mansano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vmansano@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de   Infraestrutura   de   Rede   e Servidore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nilton Aparecido Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nagarcia@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Fábrica de Software e Sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiane Suelen Aguilar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dsaguilar@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Suporte e Manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sergio Ricardo Rissatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srrissati@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de   Inteligência   de   Negócios, Integração e Desenvolvimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diogo Tavares da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dtsilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão    de    Arquivo    Público Municipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aracele Aparecida Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arosa@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Acervo Histórico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariana Souza Guimarães</t>
+  </si>
+  <si>
+    <t xml:space="preserve">msguimaraes@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Gestão Documental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodrigo Sol Moraes Cavalcanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmcavalcanti@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA MUNICIPAL DE OBRAS, ENGENHARIA E INFRAESTRUTURA DECRETO N.º 9.966/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leandro Pierin Gallina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgallina@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caique Alexandre de Oliveira Borba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cborba@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela Aparecida Braga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gapbraga@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Gestão  de  Concessão  dos Serviços de Água e Esgoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Paulo de Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jpcastro@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Planejamento Urbano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Didiane Victoria Buzinelli Inaba</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dvinaba@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor        de        Planejamento,
+Desenvolvimento      Urbano      e      Gestão      de Contrapartida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amanda Weber Minari Meniti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">awmeniti@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre Durvano da Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Manutenção de Vias Urbanas e Rurai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silvio Roberto Sentinello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Manutenção  de  Edificações Pública</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis Gustavo Barbosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Manutenção  de  Iluminação Pública</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flávio Augusto Santinon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fasantinon@olimpia.sp.gov.br </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Projetos e Obras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Augusto Gianotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jagianotto@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luís Carlos Benites Biagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Fiscalização de Obras Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricardo Alexandre da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radasilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Gerenciamento de Contratos de
+Obras Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Victor Buzzo Narcizo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Drenagem Urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Augusto Gezuato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rgezuato@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão    de    Licenciamento    e
+Regularização</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samy Ribeiro dos Santos Leandro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srsantos@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Licenciamento de Obras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela dos Santos Pasquotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gspasquotto@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Fiscalização e Regularização</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Henrique Carvalho Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhsilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor       de       Topografia       e Georreferenciamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricardo Antonio Motta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramotta@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor  de  Regularização  Fundiária  de
+Interesse Específico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sergio Oliveira Silva Carvalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scarvalho@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Convênios e Operações de Recursos Externos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre Eloi da Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aecosta@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor    de    Operacionalização    de Convênios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de   Prestação   de   Contas   e Monitoramento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Raquel de Oliveira Vittorelli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roliveira@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA MUNICIPAL DE ZELADORIA E MEIO AMBIENTE DECRETO N.º 9.839/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Paulo Morelli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jpmorelli@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrício Henrique Raimondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fhraimondo@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcio Aparecido da Silva Júnior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">masjunior@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Serviços de Zeladoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Lourenço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llourenco@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Conservação Urbana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ênio Marcos de Lima Velho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Conservação de Áreas Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Arborização e Paisagismo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Meio Ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulo Sérgio Buzzo Júnior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">psjunior@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor   de   Manutenção,   Operação   e Instalações Ambientais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Almeida Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labernardo@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Fiscalização e Licenciamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Augusto de Souza Gomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fagomes@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Educação Ambiental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaqueline M. Pereira Barbosa da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jpbsilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão  de  Proteção  e  Bem-Estar
+Animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia Sicchieri de Campos Moro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jsicchieri@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Acolhimento e Proteção Animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezio Nagamine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ezio.nagamine@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA MUNICIPAL DE SEGURANÇA, TRÂNSITO E MOBILIDADE URBANA DECRETO N.º 9.836/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinicius Claudio Zoppellari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vinicius.zoppellari@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luiz Henrique de Araújo Rocha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lhrocha@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão  de  Trânsito  e  Mobilidade
+Urbana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guilherme Vinicius da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gvsilva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Sinalização Viária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Douglas de Lima Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dlpereira@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Transporte Público e Privado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Paula da Silva Veber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apveber@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor    de    Infração,    Controle    e
+Fiscalização da Área Azul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanessa de Cassia Marretto Sbais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vmsbais@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Coordenação da Defesa
+Civil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARDA CIVIL MUNICIPAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comandante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcio Henrique Trindade Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marcio.silva@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregedor da Guarda Civil Municipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giovani Aparecido Galetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gagaletti@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouvidor da Guarda Civil Municipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROLADORIA GERAL DO MUNICÍPIO DECRETO N.º 9.824/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guilherme Sa Guimarães</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gsguimaraes@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão      Administrativa      da Controladoria Geral do Município</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graziela Miranda Eugênio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gmeugenio@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Apoio ao Sistema de Controle Interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruna de Cássia Bonilha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bcbonilha@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão   de   Controle   Interno   e Transparência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Débora Luiza Mesquita Ramos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dlramos@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Auditoria Interna e Análise de Conta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viviane de Carvalho Montagnane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vmontagnane@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chefe do Setor de Auditoria das Parcerias com o Terceiro Seto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole dos Santos Alvares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsalvares@olimpia.sp.gov.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-MAIL DE CONTATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Planejamento e Orçamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Execução Orçamentária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Tesouraria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão  de  Cadastro  e  Gestão  da
 Dívida Ativa</t>
   </si>
   <si>
-    <t xml:space="preserve">Gabriela Cardoso da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gcsilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Cadastro Imobiliário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrícia Bassi Bitencourt Gobbi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbitencourt@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Cadastro Mobiliário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrícia de Cássia Velini Bertuolo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcvelini@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Patrimônio Imobiliário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruna Camioto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bcamioto@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Dívida Ativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frederico Camioto Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fcamioto@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Fiscalização Tributária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renato Luis Pivello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rlpivello@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Tributos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosicler Berti Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rbsantos@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Fiscalização de Posturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deise Cristina Lopes Valério</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dclvalerio@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Posturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleber Luis Gonsaga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clgonsaga@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRETARIA MUNICIPAL DE GESTÃO E CIDADE INTELIGENTE DECRETO N.º 9.843/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Mena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max.mena@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Gestão  de  Recursos
-Humanos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandro de Campos Magalhães</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smagalhaes@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Folha de Pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thaina Bartholomeu Cordon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tbcordon@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe      do      Setor      de      Treinamento      e
-Desenvolvimento Humano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taiga Renata da Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tarcruz@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor   de  Serviço  Especializado  em Segurança e Medicina do Trabalho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michelli da Silva Camargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">michelli.camargo@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Gestão  de  Vínculos,  Atos  e Sistemas de Escrituração Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isabela Recco de Almeida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">irecco@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Gestão e Planejamento de Compras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karolini Escobar de Souza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kesouza@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Planejamento e Formalização das Contratações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Laura Rosa Machado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">almachado@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Compras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thais da Silva Fernandes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tsfernandes@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Licitações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carolina Feitosa Ferezin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cfferezin@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Gestão Contratual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Paula Rodrigues Bertolino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arodrigues@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Gestão de Contratos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lígia Dias de oliveira Bianchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ldoliveira@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Fiscalização de Contratos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiane da Fonseca Trinca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dftrinca@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Contratos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariana Daroz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mdaroz@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Gestão Logística</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helton Jose Quilles Rodrigues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hjrodrigues@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Almoxarifado e Distribuição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Márcio Gláucio Ribeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgribeiro@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natali Aparecida Souza Camargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nacamargo@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Gestão Operacional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andre Luiz Alves da Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alcosta@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Patrimônio Mobiliário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Mateus A. Martins dos Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lmasantos@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Controle  e  Manutenção  de Frotas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio e Atendimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julio Cezar dos Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jcsantos@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Tecnologia da Informação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Ishikawa Mansano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vmansano@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Infraestrutura   de   Rede   e Servidores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nilton Aparecido Garcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nagarcia@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Fábrica de Software e Sistemas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiane Suelen Aguilar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dsaguilar@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Suporte e Manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sergio Ricardo Rissatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">srrissati@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Inteligência   de   Negócios, Integração e Desenvolvimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diogo Tavares da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dtsilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor    da    Divisão    de    Arquivo    Público Municipal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aracele Aparecida Rosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arosa@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Acervo Histórico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariana Souza Guimarães</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msguimaraes@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Gestão Documental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodrigo Sol Moraes Cavalcanti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rmcavalcanti@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRETARIA MUNICIPAL DE OBRAS, ENGENHARIA E INFRAESTRUTURA DECRETO N.º 9.966/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leandro Pierin Gallina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lgallina@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caique Alexandre de Oliveira Borba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cborba@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriela Aparecida Braga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gapbraga@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Gestão  de  Concessão  dos Serviços de Água e Esgoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Paulo de Castro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jpcastro@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Planejamento Urbano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didiane Victoria Buzinelli Inaba</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> dvinaba@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe        do        Setor        de        Planejamento,
-Desenvolvimento      Urbano      e      Gestão      de Contrapartidas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amanda Weber Minari Meniti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">awmeniti@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Manutenção</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre Durvano da Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Manutenção de Vias Urbanas e Rurais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silvio Roberto Sentinello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Manutenção  de  Edificações Públicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis Gustavo Barbosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Manutenção  de  Iluminação Pública</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flávio Augusto Santinon</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fasantinon@olimpia.sp.gov.br </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Projetos e Obras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">José Augusto Gianotto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jagianotto@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Projetos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luís Carlos Benites Biagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Fiscalização de Obras Públicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricardo Alexandre da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">radasilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Gerenciamento de Contratos de
-Obras Públicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Victor Buzzo Narcizo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Drenagem Urbana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Augusto Gezuato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rgezuato@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor    da    Divisão    de    Licenciamento    e
-Regularização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samy Ribeiro dos Santos Leandro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">srsantos@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Licenciamento de Obras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriela dos Santos Pasquotto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gspasquotto@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Fiscalização e Regularização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando Henrique Carvalho Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fhsilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe       do       Setor       de       Topografia       e Georreferenciamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricardo Antonio Motta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ramotta@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe  do  Setor  de  Regularização  Fundiária  de
-Interesse Específico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sergio Oliveira Silva Carvalho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scarvalho@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Convênios e Operações de Recursos Externos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre Eloi da Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aecosta@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Operacionalização    de Convênios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Prestação   de   Contas   e Monitoramento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Raquel de Oliveira Vittorelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roliveira@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRETARIA MUNICIPAL DE ZELADORIA E MEIO AMBIENTE DECRETO N.º 9.839/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Paulo Morelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jpmorelli@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrício Henrique Raimondo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fhraimondo@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcio Aparecido da Silva Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">masjunior@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Serviços de Zeladoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Lourenço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">llourenco@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Conservação Urbana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ênio Marcos de Lima Velho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Conservação de Áreas Verdes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Arborização e Paisagismo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Meio Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paulo Sérgio Buzzo Júnior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">psjunior@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe   do   Setor   de   Manutenção,   Operação   e Instalações Ambientais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Almeida Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labernardo@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Fiscalização e Licenciamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando Augusto de Souza Gomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fagomes@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Educação Ambiental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaqueline M. Pereira Barbosa da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jpbsilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Proteção  e  Bem-Estar
-Animal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julia Sicchieri de Campos Moro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jsicchieri@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Acolhimento e Proteção Animal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezio Nagamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ezio.nagamine@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRETARIA MUNICIPAL DE SEGURANÇA, TRÂNSITO E MOBILIDADE URBANA DECRETO N.º 9.836/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinicius Claudio Zoppellari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vinicius.zoppellari@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luiz Henrique de Araújo Rocha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lhrocha@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor  da  Divisão  de  Trânsito  e  Mobilidade
-Urbana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guilherme Vinicius da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gvsilva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Sinalização Viária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Douglas de Lima Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dlpereira@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Transporte Público e Privado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Paula da Silva Veber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apveber@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe    do    Setor    de    Infração,    Controle    e
-Fiscalização da Área Azul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanessa de Cassia Marretto Sbais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vmsbais@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor da Divisão de Coordenação da Defesa
-Civil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARDA CIVIL MUNICIPAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comandante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcio Henrique Trindade Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marcio.silva@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corregedor da Guarda Civil Municipal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giovani Aparecido Galetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gagaletti@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ouvidor da Guarda Civil Municipal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROLADORIA GERAL DO MUNICÍPIO DECRETO N.º 9.824/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controlador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guilherme Sa Guimarães</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gsguimaraes@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor      da      Divisão      Administrativa      da Controladoria Geral do Município</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graziela Miranda Eugênio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gmeugenio@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Apoio ao Sistema de Controle Interno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruna de Cássia Bonilha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bcbonilha@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor   da   Divisão   de   Controle   Interno   e Transparência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Débora Luiza Mesquita Ramos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dlramos@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Auditoria Interna e Análise de Contas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viviane de Carvalho Montagnane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vmontagnane@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chefe do Setor de Auditoria das Parcerias com o Terceiro Setor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole dos Santos Alvares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsalvares@olimpia.sp.gov.br</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-MAIL DE CONTATO</t>
+    <t xml:space="preserve">Setor de Cadastro Imobiliário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Cadastro Mobiliário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Fiscalização Tributária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Tributos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão de Fiscalização de Posturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor de Posturas</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2399,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2383,7 +2407,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2399,7 +2423,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2463,7 +2487,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2471,7 +2495,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2694,7 +2718,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.33"/>
@@ -3537,7 +3561,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -3900,7 +3924,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="82.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -3942,24 +3966,24 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>56.838</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>56.545</v>
@@ -3967,10 +3991,10 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>56.547</v>
@@ -3978,91 +4002,91 @@
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>56.546</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>56.541</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>56.543</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>189</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>56.817</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>56.542</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>195</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>56.544</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -4083,87 +4107,87 @@
         <v>20</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>200</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>56.916</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>204</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>56.918</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>56.917</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>209</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>210</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>56.919</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>213</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>56.92</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
@@ -4184,121 +4208,121 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>56.839</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>56.84</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>56.843</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>56.841</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>231</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>56.844</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>56.842</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>56.845</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -4319,89 +4343,89 @@
         <v>20</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>56.942</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>56.945</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>56.946</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>56.947</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>56.943</v>
@@ -4409,42 +4433,42 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>56.948</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>56.949</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -4452,80 +4476,80 @@
     </row>
     <row r="46" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>265</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>57.597</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>267</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>268</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>56.95</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>56.951</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>274</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>56.944</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>56.952</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>56.953</v>
@@ -4533,16 +4557,16 @@
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>281</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>282</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>56.954</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -4574,7 +4598,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -4586,7 +4610,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -4602,7 +4626,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4610,202 +4634,202 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C3" s="30"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C5" s="31" t="n">
         <v>57.119</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>289</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>290</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>56.968</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>292</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>293</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>56.969</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="C10" s="31" t="n">
         <v>56.972</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="C11" s="31" t="n">
         <v>56.961</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>303</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>304</v>
       </c>
       <c r="C12" s="31" t="n">
         <v>56.973</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>307</v>
       </c>
       <c r="C13" s="31" t="n">
         <v>56.974</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>310</v>
       </c>
       <c r="C14" s="31" t="n">
         <v>56.975</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>313</v>
       </c>
       <c r="C15" s="31" t="n">
         <v>56.976</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>315</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>316</v>
       </c>
       <c r="C16" s="31" t="n">
         <v>56.977</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>319</v>
       </c>
       <c r="C17" s="31" t="n">
         <v>56.978</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="30"/>
@@ -4813,10 +4837,10 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>325</v>
       </c>
       <c r="C21" s="31" t="n">
         <v>56.962</v>
@@ -4824,80 +4848,80 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>327</v>
       </c>
       <c r="C22" s="31" t="n">
         <v>56.979</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>330</v>
       </c>
       <c r="C23" s="31" t="n">
         <v>56.98</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>333</v>
       </c>
       <c r="C24" s="31" t="n">
         <v>56.981</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>336</v>
       </c>
       <c r="C25" s="31" t="n">
         <v>56.963</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>339</v>
       </c>
       <c r="C26" s="31" t="n">
         <v>56.982</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>341</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>342</v>
       </c>
       <c r="C27" s="31" t="n">
         <v>56.983</v>
@@ -4905,163 +4929,163 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>343</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>344</v>
       </c>
       <c r="C28" s="31" t="n">
         <v>56.984</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>346</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>347</v>
       </c>
       <c r="C29" s="31" t="n">
         <v>56.985</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>350</v>
       </c>
       <c r="C30" s="31" t="n">
         <v>57724</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="C31" s="31" t="n">
         <v>57.039</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="D32" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>359</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>360</v>
       </c>
       <c r="C33" s="31" t="n">
         <v>56.988</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="C35" s="31" t="n">
         <v>56.965</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>366</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>367</v>
       </c>
       <c r="C36" s="31" t="n">
         <v>56.989</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>370</v>
       </c>
       <c r="C37" s="31" t="n">
         <v>56.99</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>373</v>
       </c>
       <c r="C38" s="31" t="n">
         <v>56.966</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>375</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>376</v>
       </c>
       <c r="C39" s="31" t="n">
         <v>56.991</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5090,7 +5114,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -5102,7 +5126,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -5123,33 +5147,33 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="C4" s="33" t="n">
         <v>56.868</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>384</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>385</v>
       </c>
       <c r="C5" s="33" t="n">
         <v>56.873</v>
@@ -5157,90 +5181,90 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>386</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>387</v>
       </c>
       <c r="C6" s="33" t="n">
         <v>56.874</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>390</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>56.869</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>393</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>394</v>
       </c>
       <c r="C8" s="33" t="n">
         <v>56.875</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>396</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>397</v>
       </c>
       <c r="C9" s="33" t="n">
         <v>56.876</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10" s="33" t="n">
         <v>56.877</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>403</v>
       </c>
       <c r="C12" s="33" t="n">
         <v>56.87</v>
@@ -5248,10 +5272,10 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>405</v>
       </c>
       <c r="C13" s="33" t="n">
         <v>56.878</v>
@@ -5259,94 +5283,94 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>406</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>407</v>
       </c>
       <c r="C14" s="33" t="n">
         <v>56.879</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>409</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>410</v>
       </c>
       <c r="C15" s="33" t="n">
         <v>56.88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>413</v>
       </c>
       <c r="C16" s="33" t="n">
         <v>56.871</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>415</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>416</v>
       </c>
       <c r="C17" s="33" t="n">
         <v>56.881</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>418</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>419</v>
       </c>
       <c r="C18" s="33" t="n">
         <v>56.882</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>421</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>422</v>
       </c>
       <c r="C19" s="33" t="n">
         <v>56.883</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>424</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>425</v>
       </c>
       <c r="C20" s="33" t="n">
         <v>56.884</v>
@@ -5355,77 +5379,77 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C21" s="33" t="n">
         <v>56.888</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C22" s="33" t="n">
         <v>56.885</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C23" s="33" t="n">
         <v>56.872</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C24" s="33" t="n">
         <v>56.886</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C25" s="34" t="n">
         <v>56.887</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="35" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B26" s="35"/>
       <c r="C26" s="35"/>
@@ -5446,193 +5470,193 @@
         <v>20</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>57.042</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>57.208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>57.047</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>57.059</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>57.048</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>57.049</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>57.05</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>57.051</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>57.044</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>57.052</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>57.045</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>57.053</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,7 +5683,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -5671,7 +5695,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -5692,219 +5716,219 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>56.89</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>56.897</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>56.898</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>56.899</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>56.9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>56.891</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>56.901</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>56.902</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>56.903</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>56.892</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>56.904</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>56.905</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>56.893</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>56.906</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5912,175 +5936,175 @@
         <v>77</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>57.232</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>56.894</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>56.907</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>56.909</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>56.895</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>56.91</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>56.911</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>56.912</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>56.913</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>56.896</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>56.914</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>56.915</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6111,7 +6135,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="72.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -6123,7 +6147,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -6144,89 +6168,89 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>57.019</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>57.024</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>57.025</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>57.02</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>57.026</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>57.021</v>
@@ -6234,10 +6258,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>57.027</v>
@@ -6245,10 +6269,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>57.028</v>
@@ -6256,38 +6280,38 @@
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>57.029</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>57.022</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>57.03</v>
@@ -6295,24 +6319,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>57.031</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>57.032</v>
@@ -6323,58 +6347,58 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>57.033</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>57.023</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>57.034</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>57.035</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>42</v>
@@ -6382,30 +6406,30 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>57.036</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>57.037</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -6413,16 +6437,16 @@
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>57.6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>52</v>
@@ -6430,23 +6454,23 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>57.601</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>56</v>
@@ -6454,7 +6478,7 @@
     </row>
     <row r="26" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -6478,11 +6502,11 @@
         <v>20</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>64</v>
@@ -6490,16 +6514,16 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>56.921</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>67</v>
@@ -6507,16 +6531,16 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>56.924</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>70</v>
@@ -6524,16 +6548,16 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>56.922</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>73</v>
@@ -6541,10 +6565,10 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>56.925</v>
@@ -6555,7 +6579,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -6565,37 +6589,37 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>56.923</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>57.421</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>82</v>
@@ -6603,16 +6627,16 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>56.926</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>85</v>
@@ -6620,44 +6644,44 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>56.927</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>57.419</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>57.42</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>90</v>
@@ -6668,7 +6692,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H44" s="2" t="s">
         <v>99</v>
       </c>
@@ -6718,7 +6742,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
@@ -6730,7 +6754,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -6751,93 +6775,93 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>56.937</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>56.938</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>56.94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>56.939</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>56.941</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -6855,40 +6879,40 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>55.481</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -6906,85 +6930,85 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>56.933</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>56.934</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>56.932</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>56.936</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>56.935</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7012,7 +7036,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.21"/>
@@ -7022,7 +7046,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -7039,7 +7063,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7047,52 +7071,52 @@
         <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>57.042</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>445</v>
+        <v>700</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>446</v>
+        <v>701</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>57.208</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>449</v>
+        <v>702</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -7100,142 +7124,142 @@
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>57.047</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>453</v>
+        <v>703</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>57.059</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>455</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>457</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>57.048</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>458</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>460</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>57.049</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>461</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>463</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>57.05</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>57.051</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>467</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>469</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>57.044</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>471</v>
+        <v>707</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>57.052</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>473</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>475</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>57.045</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>477</v>
+        <v>709</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>57.053</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
